--- a/esyluban/templates/DataTables/monsters.xlsx
+++ b/esyluban/templates/DataTables/monsters.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string#ref=text.TbText</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>史莱姆</t>
+          <t>/monster_2001_name</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -504,7 +504,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>哥布林</t>
+          <t>/monster_2002_name</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -520,7 +520,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>巨魔</t>
+          <t>/monster_2003_name</t>
         </is>
       </c>
       <c r="D6" t="n">
